--- a/BWI/bestwine_output/bestwine_Paraguay.xlsx
+++ b/BWI/bestwine_output/bestwine_Paraguay.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA69"/>
+  <dimension ref="A1:AA71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -8141,6 +8141,232 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Casa Modiga S.a.</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Casa Modiga S.a.</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>29470</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Asunción</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Asunción</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>7475 Avenida Doctor Guido Boggiani</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>001419</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>https://modiga.com.py</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>info@modiga.com.py</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>+595 21 237 6787</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>1955</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>80001423-5</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/m%C3%B3diga-s-a/</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/casamodiga</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/modiga.py</t>
+        </is>
+      </c>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr"/>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>Francisco José Gómez Moro</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr"/>
+      <c r="Z70" s="2" t="inlineStr"/>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/francisco-jos%C3%A9-g%C3%B3mez-moro-1ba807143/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Casa Modiga S.a.</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Casa Modiga S.a.</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>29470</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Asunción</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Asunción</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>7475 Avenida Doctor Guido Boggiani</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>001419</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>https://modiga.com.py</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>info@modiga.com.py</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>+595 21 237 6787</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>1955</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>80001423-5</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/m%C3%B3diga-s-a/</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/casamodiga</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/modiga.py</t>
+        </is>
+      </c>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr"/>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>Gilberto Mutti</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing And Import Manager</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr"/>
+      <c r="Z71" s="2" t="inlineStr"/>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gilberto-mutti-4152b0a6/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Paraguay.xlsx
+++ b/BWI/bestwine_output/bestwine_Paraguay.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA71"/>
+  <dimension ref="A1:AA73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -8367,6 +8367,232 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Casa Modiga S.a.</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Casa Modiga S.a.</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>29470</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Asunción</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Asunción</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>7475 Avenida Doctor Guido Boggiani</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>001419</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>https://modiga.com.py</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>info@modiga.com.py</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>+595 21 237 6787</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>1955</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>80001423-5</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/m%C3%B3diga-s-a/</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/casamodiga</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/modiga.py</t>
+        </is>
+      </c>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr"/>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>Francisco José Gómez Moro</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr"/>
+      <c r="Z72" s="2" t="inlineStr"/>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/francisco-jos%C3%A9-g%C3%B3mez-moro-1ba807143/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Casa Modiga S.a.</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Casa Modiga S.a.</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>29470</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Asunción</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Asunción</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>7475 Avenida Doctor Guido Boggiani</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>001419</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>https://modiga.com.py</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>info@modiga.com.py</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>+595 21 237 6787</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>1955</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>80001423-5</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/m%C3%B3diga-s-a/</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/casamodiga</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/modiga.py</t>
+        </is>
+      </c>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr"/>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>Gilberto Mutti</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing And Import Manager</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr"/>
+      <c r="Z73" s="2" t="inlineStr"/>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gilberto-mutti-4152b0a6/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Paraguay.xlsx
+++ b/BWI/bestwine_output/bestwine_Paraguay.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA73"/>
+  <dimension ref="A1:AA75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -8593,6 +8593,232 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Casa Modiga S.a.</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Casa Modiga S.a.</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>29470</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Asunción</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Asunción</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>7475 Avenida Doctor Guido Boggiani</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>001419</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>https://modiga.com.py</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>info@modiga.com.py</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>+595 21 237 6787</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>1955</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>80001423-5</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/m%C3%B3diga-s-a/</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/casamodiga</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/modiga.py</t>
+        </is>
+      </c>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr"/>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>Francisco José Gómez Moro</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr"/>
+      <c r="Z74" s="2" t="inlineStr"/>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/francisco-jos%C3%A9-g%C3%B3mez-moro-1ba807143/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Casa Modiga S.a.</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Casa Modiga S.a.</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>29470</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Asunción</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Asunción</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>7475 Avenida Doctor Guido Boggiani</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>001419</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>https://modiga.com.py</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>info@modiga.com.py</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>+595 21 237 6787</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>1955</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>80001423-5</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/m%C3%B3diga-s-a/</t>
+        </is>
+      </c>
+      <c r="S75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/casamodiga</t>
+        </is>
+      </c>
+      <c r="T75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/modiga.py</t>
+        </is>
+      </c>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr"/>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>Gilberto Mutti</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing And Import Manager</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr"/>
+      <c r="Z75" s="2" t="inlineStr"/>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gilberto-mutti-4152b0a6/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Paraguay.xlsx
+++ b/BWI/bestwine_output/bestwine_Paraguay.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA75"/>
+  <dimension ref="A1:AA77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -8819,6 +8819,232 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Casa Modiga S.a.</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Casa Modiga S.a.</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>29470</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Asunción</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Asunción</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>7475 Avenida Doctor Guido Boggiani</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>001419</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>https://modiga.com.py</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>info@modiga.com.py</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>+595 21 237 6787</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>1955</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>80001423-5</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/m%C3%B3diga-s-a/</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/casamodiga</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/modiga.py</t>
+        </is>
+      </c>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr"/>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>Francisco José Gómez Moro</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr"/>
+      <c r="Z76" s="2" t="inlineStr"/>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/francisco-jos%C3%A9-g%C3%B3mez-moro-1ba807143/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Casa Modiga S.a.</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Casa Modiga S.a.</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>29470</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Asunción</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Asunción</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>7475 Avenida Doctor Guido Boggiani</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>001419</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>https://modiga.com.py</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>info@modiga.com.py</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>+595 21 237 6787</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>1955</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>80001423-5</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/m%C3%B3diga-s-a/</t>
+        </is>
+      </c>
+      <c r="S77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/casamodiga</t>
+        </is>
+      </c>
+      <c r="T77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/modiga.py</t>
+        </is>
+      </c>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr"/>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>Gilberto Mutti</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing And Import Manager</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr"/>
+      <c r="Z77" s="2" t="inlineStr"/>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gilberto-mutti-4152b0a6/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
